--- a/ValueSet-dk-marital-status.xlsx
+++ b/ValueSet-dk-marital-status.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.1</t>
+    <t>2.0.0</t>
   </si>
   <si>
     <t>Name</t>

--- a/ValueSet-dk-marital-status.xlsx
+++ b/ValueSet-dk-marital-status.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0</t>
+    <t>1.1.1</t>
   </si>
   <si>
     <t>Name</t>

--- a/ValueSet-dk-marital-status.xlsx
+++ b/ValueSet-dk-marital-status.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0</t>
+    <t>2.1.0</t>
   </si>
   <si>
     <t>Name</t>

--- a/ValueSet-dk-marital-status.xlsx
+++ b/ValueSet-dk-marital-status.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="38">
   <si>
     <t>Property</t>
   </si>
@@ -35,9 +35,6 @@
   </si>
   <si>
     <t>Name</t>
-  </si>
-  <si>
-    <t>DK Marital Status Codes</t>
   </si>
   <si>
     <t>Title</t>
@@ -299,94 +296,92 @@
       <c r="A4" t="s" s="2">
         <v>6</v>
       </c>
-      <c r="B4" t="s" s="2">
-        <v>7</v>
-      </c>
+      <c r="B4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
+        <v>7</v>
+      </c>
+      <c r="B5" t="s" s="2">
         <v>8</v>
-      </c>
-      <c r="B5" t="s" s="2">
-        <v>9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
+        <v>9</v>
+      </c>
+      <c r="B6" t="s" s="2">
         <v>10</v>
-      </c>
-      <c r="B6" t="s" s="2">
-        <v>11</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s" s="2">
         <v>12</v>
-      </c>
-      <c r="B7" t="s" s="2">
-        <v>13</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B8" t="s" s="2">
         <v>14</v>
-      </c>
-      <c r="B8" t="s" s="2">
-        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="B9" t="s" s="2">
         <v>16</v>
-      </c>
-      <c r="B9" t="s" s="2">
-        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="B10" t="s" s="2">
         <v>18</v>
-      </c>
-      <c r="B10" t="s" s="2">
-        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="B11" t="s" s="2">
         <v>20</v>
-      </c>
-      <c r="B11" t="s" s="2">
-        <v>21</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B12" t="s" s="2">
         <v>22</v>
-      </c>
-      <c r="B12" t="s" s="2">
-        <v>23</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="B14" t="s" s="2">
         <v>25</v>
-      </c>
-      <c r="B14" t="s" s="2">
-        <v>26</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
+        <v>26</v>
+      </c>
+      <c r="B15" t="s" s="2">
         <v>27</v>
-      </c>
-      <c r="B15" t="s" s="2">
-        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -405,12 +400,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -429,42 +424,42 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="B2" t="s" s="2">
         <v>32</v>
-      </c>
-      <c r="B2" t="s" s="2">
-        <v>33</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="B3" t="s" s="2">
         <v>34</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>35</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B5" t="s" s="2">
         <v>37</v>
-      </c>
-      <c r="B5" t="s" s="2">
-        <v>38</v>
       </c>
     </row>
   </sheetData>

--- a/ValueSet-dk-marital-status.xlsx
+++ b/ValueSet-dk-marital-status.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.1.0</t>
+    <t>2.2.0</t>
   </si>
   <si>
     <t>Name</t>

--- a/ValueSet-dk-marital-status.xlsx
+++ b/ValueSet-dk-marital-status.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2019-11-01T09:29:23+11:00</t>
+    <t>2023-04-18T12:02:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-marital-status.xlsx
+++ b/ValueSet-dk-marital-status.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-18T12:02:45+00:00</t>
+    <t>2023-04-24T21:40:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-marital-status.xlsx
+++ b/ValueSet-dk-marital-status.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-24T21:40:58+00:00</t>
+    <t>2019-11-01T09:29:23+11:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-marital-status.xlsx
+++ b/ValueSet-dk-marital-status.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2019-11-01T09:29:23+11:00</t>
+    <t>2023-04-30T20:59:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-marital-status.xlsx
+++ b/ValueSet-dk-marital-status.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-30T20:59:20+00:00</t>
+    <t>2023-04-30T21:23:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-marital-status.xlsx
+++ b/ValueSet-dk-marital-status.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-30T21:23:00+00:00</t>
+    <t>2023-05-05T00:02:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-marital-status.xlsx
+++ b/ValueSet-dk-marital-status.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.2.0</t>
+    <t>3.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T00:02:52+00:00</t>
+    <t>2023-11-28T12:13:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -249,10 +249,10 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyBorder="true" applyFill="true" applyFont="true">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyBorder="true" applyFill="true" applyAlignment="true" applyFont="true">
       <alignment vertical="top" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="true">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="true" applyAlignment="true">
       <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>

--- a/ValueSet-dk-marital-status.xlsx
+++ b/ValueSet-dk-marital-status.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-28T12:13:03+00:00</t>
+    <t>2023-11-30T13:40:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-marital-status.xlsx
+++ b/ValueSet-dk-marital-status.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-30T13:40:49+00:00</t>
+    <t>2023-11-30T14:55:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-marital-status.xlsx
+++ b/ValueSet-dk-marital-status.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-30T14:55:40+00:00</t>
+    <t>2023-12-01T12:31:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-marital-status.xlsx
+++ b/ValueSet-dk-marital-status.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-01T12:31:40+00:00</t>
+    <t>2023-12-01T13:42:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-marital-status.xlsx
+++ b/ValueSet-dk-marital-status.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.0.0</t>
+    <t>3.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-01T13:42:49+00:00</t>
+    <t>2023-12-19T10:28:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-marital-status.xlsx
+++ b/ValueSet-dk-marital-status.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-19T10:28:26+00:00</t>
+    <t>2023-12-19T10:34:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-marital-status.xlsx
+++ b/ValueSet-dk-marital-status.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-19T10:34:37+00:00</t>
+    <t>2024-01-06T18:57:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-marital-status.xlsx
+++ b/ValueSet-dk-marital-status.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-06T18:57:36+00:00</t>
+    <t>2024-01-08T22:02:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-marital-status.xlsx
+++ b/ValueSet-dk-marital-status.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.1.0</t>
+    <t>3.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-08T22:02:06+00:00</t>
+    <t>2024-01-08T22:02:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-marital-status.xlsx
+++ b/ValueSet-dk-marital-status.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-08T22:02:40+00:00</t>
+    <t>2024-03-19T10:43:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-marital-status.xlsx
+++ b/ValueSet-dk-marital-status.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-19T10:43:29+00:00</t>
+    <t>2024-04-03T07:46:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-marital-status.xlsx
+++ b/ValueSet-dk-marital-status.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T07:46:18+00:00</t>
+    <t>2024-04-03T10:16:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-marital-status.xlsx
+++ b/ValueSet-dk-marital-status.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T10:16:02+00:00</t>
+    <t>2024-04-10T06:34:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -70,7 +70,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>HL7 Denmark (http://www.hl7.dk, jenskristianvilladsen@gmail.com)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/ValueSet-dk-marital-status.xlsx
+++ b/ValueSet-dk-marital-status.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T06:34:41+00:00</t>
+    <t>2024-04-11T09:53:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-marital-status.xlsx
+++ b/ValueSet-dk-marital-status.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-11T09:53:59+00:00</t>
+    <t>2024-04-12T06:23:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-marital-status.xlsx
+++ b/ValueSet-dk-marital-status.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T06:23:14+00:00</t>
+    <t>2024-04-16T10:58:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-marital-status.xlsx
+++ b/ValueSet-dk-marital-status.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-16T10:58:26+00:00</t>
+    <t>2024-04-18T15:20:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-marital-status.xlsx
+++ b/ValueSet-dk-marital-status.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-18T15:20:26+00:00</t>
+    <t>2024-04-18T15:27:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-marital-status.xlsx
+++ b/ValueSet-dk-marital-status.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-18T15:27:51+00:00</t>
+    <t>2024-04-22T11:01:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-marital-status.xlsx
+++ b/ValueSet-dk-marital-status.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-22T11:01:11+00:00</t>
+    <t>2024-04-22T12:03:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-marital-status.xlsx
+++ b/ValueSet-dk-marital-status.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-22T12:03:36+00:00</t>
+    <t>2024-04-22T13:38:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-marital-status.xlsx
+++ b/ValueSet-dk-marital-status.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-22T13:38:01+00:00</t>
+    <t>2024-04-23T08:24:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-marital-status.xlsx
+++ b/ValueSet-dk-marital-status.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-23T08:24:27+00:00</t>
+    <t>2024-04-23T10:50:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-marital-status.xlsx
+++ b/ValueSet-dk-marital-status.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-23T10:50:14+00:00</t>
+    <t>2024-04-23T18:15:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-marital-status.xlsx
+++ b/ValueSet-dk-marital-status.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-23T18:15:55+00:00</t>
+    <t>2024-05-02T12:47:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-marital-status.xlsx
+++ b/ValueSet-dk-marital-status.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-02T12:47:39+00:00</t>
+    <t>2024-05-03T13:03:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-marital-status.xlsx
+++ b/ValueSet-dk-marital-status.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-03T13:03:24+00:00</t>
+    <t>2024-05-06T06:35:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-marital-status.xlsx
+++ b/ValueSet-dk-marital-status.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T06:35:09+00:00</t>
+    <t>2024-05-06T07:49:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-marital-status.xlsx
+++ b/ValueSet-dk-marital-status.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.2.0</t>
+    <t>3.3.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T07:49:19+00:00</t>
+    <t>2024-05-06T14:14:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-marital-status.xlsx
+++ b/ValueSet-dk-marital-status.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T14:14:33+00:00</t>
+    <t>2024-05-10T08:40:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-marital-status.xlsx
+++ b/ValueSet-dk-marital-status.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-10T08:40:47+00:00</t>
+    <t>2024-05-10T19:12:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-marital-status.xlsx
+++ b/ValueSet-dk-marital-status.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-10T19:12:38+00:00</t>
+    <t>2024-05-12T08:40:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-marital-status.xlsx
+++ b/ValueSet-dk-marital-status.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-12T08:40:34+00:00</t>
+    <t>2024-05-12T08:41:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-marital-status.xlsx
+++ b/ValueSet-dk-marital-status.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-12T08:41:58+00:00</t>
+    <t>2024-05-12T09:45:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-marital-status.xlsx
+++ b/ValueSet-dk-marital-status.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-12T09:45:49+00:00</t>
+    <t>2024-05-12T11:37:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-marital-status.xlsx
+++ b/ValueSet-dk-marital-status.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-12T11:37:02+00:00</t>
+    <t>2024-06-03T20:51:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-marital-status.xlsx
+++ b/ValueSet-dk-marital-status.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-03T20:51:53+00:00</t>
+    <t>2024-06-25T21:12:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-marital-status.xlsx
+++ b/ValueSet-dk-marital-status.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-25T21:12:53+00:00</t>
+    <t>2024-06-25T21:21:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-marital-status.xlsx
+++ b/ValueSet-dk-marital-status.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-25T21:21:07+00:00</t>
+    <t>2024-06-25T21:20:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-marital-status.xlsx
+++ b/ValueSet-dk-marital-status.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-25T21:20:43+00:00</t>
+    <t>2024-06-25T21:42:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-marital-status.xlsx
+++ b/ValueSet-dk-marital-status.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-25T21:42:34+00:00</t>
+    <t>2024-06-26T14:36:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-marital-status.xlsx
+++ b/ValueSet-dk-marital-status.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-26T14:36:19+00:00</t>
+    <t>2024-06-27T10:47:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-marital-status.xlsx
+++ b/ValueSet-dk-marital-status.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-27T10:47:07+00:00</t>
+    <t>2024-08-11T15:57:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-marital-status.xlsx
+++ b/ValueSet-dk-marital-status.xlsx
@@ -7,8 +7,8 @@
   </bookViews>
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
-    <sheet name="Include ValueSets" r:id="rId4" sheetId="2"/>
-    <sheet name="Include from DK Marital Statu" r:id="rId5" sheetId="3"/>
+    <sheet name="Include ValueSet #0" r:id="rId4" sheetId="2"/>
+    <sheet name="Include #1" r:id="rId5" sheetId="3"/>
   </sheets>
 </workbook>
 </file>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-11T15:57:41+00:00</t>
+    <t>2024-10-17T12:12:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-marital-status.xlsx
+++ b/ValueSet-dk-marital-status.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-17T12:12:58+00:00</t>
+    <t>2024-10-17T12:15:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-marital-status.xlsx
+++ b/ValueSet-dk-marital-status.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-17T12:15:17+00:00</t>
+    <t>2024-10-18T06:07:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-marital-status.xlsx
+++ b/ValueSet-dk-marital-status.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-18T06:07:37+00:00</t>
+    <t>2024-10-27T12:31:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-marital-status.xlsx
+++ b/ValueSet-dk-marital-status.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-27T12:31:37+00:00</t>
+    <t>2024-11-04T14:15:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-marital-status.xlsx
+++ b/ValueSet-dk-marital-status.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.3.0</t>
+    <t>3.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-04T14:15:57+00:00</t>
+    <t>2024-11-04T14:58:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-marital-status.xlsx
+++ b/ValueSet-dk-marital-status.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-04T14:58:42+00:00</t>
+    <t>2024-11-04T15:07:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-marital-status.xlsx
+++ b/ValueSet-dk-marital-status.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-04T15:07:28+00:00</t>
+    <t>2024-11-05T12:45:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-marital-status.xlsx
+++ b/ValueSet-dk-marital-status.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.4.0</t>
+    <t>3.3.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-05T12:45:46+00:00</t>
+    <t>2024-11-15T12:49:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-marital-status.xlsx
+++ b/ValueSet-dk-marital-status.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-15T12:49:28+00:00</t>
+    <t>2024-11-15T13:03:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-marital-status.xlsx
+++ b/ValueSet-dk-marital-status.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-15T13:03:47+00:00</t>
+    <t>2024-11-29T07:41:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-marital-status.xlsx
+++ b/ValueSet-dk-marital-status.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-29T07:41:39+00:00</t>
+    <t>2024-11-29T10:20:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-marital-status.xlsx
+++ b/ValueSet-dk-marital-status.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-29T10:20:07+00:00</t>
+    <t>2024-12-11T08:38:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-marital-status.xlsx
+++ b/ValueSet-dk-marital-status.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-11T08:38:49+00:00</t>
+    <t>2024-12-11T09:50:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-marital-status.xlsx
+++ b/ValueSet-dk-marital-status.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.3.0</t>
+    <t>3.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-11T09:50:58+00:00</t>
+    <t>2024-12-16T15:09:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-marital-status.xlsx
+++ b/ValueSet-dk-marital-status.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-16T15:09:03+00:00</t>
+    <t>2024-12-16T15:16:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-marital-status.xlsx
+++ b/ValueSet-dk-marital-status.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-16T15:16:17+00:00</t>
+    <t>2024-12-16T15:31:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
